--- a/sheets/대금율보/검수/신고산타령 (b1_116_2).xlsx
+++ b/sheets/대금율보/검수/신고산타령 (b1_116_2).xlsx
@@ -1885,8 +1885,7 @@
         <is>
           <t xml:space="preserve">淋㳞
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
@@ -1936,11 +1935,7 @@
           <t xml:space="preserve">어랑</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
@@ -2078,8 +2073,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -2091,8 +2085,7 @@
         <is>
           <t xml:space="preserve">淋㳞
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -2196,8 +2189,7 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">

--- a/sheets/대금율보/검수/신고산타령 (b1_116_2).xlsx
+++ b/sheets/대금율보/검수/신고산타령 (b1_116_2).xlsx
@@ -1832,16 +1832,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       <c r="D5" s="21"/>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       <c r="D6" s="21"/>
       <c r="E6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2244,6 +2244,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>